--- a/Tools/_test_corpus/fixtures/im-1324740.xlsx
+++ b/Tools/_test_corpus/fixtures/im-1324740.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\source\repos\RapidReconciler-AI\.claude\worktrees\recursing-williamson-0f6630\Tools\_test_corpus\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{764F6B1A-8F1A-4B9F-B607-C0FC2D178972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6948279-FD4C-4A1C-A2F4-F486DA8CF52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1D67BB71-3833-4A0A-9B2A-45CF1926B75B}"/>
+    <workbookView xWindow="2220" yWindow="720" windowWidth="22275" windowHeight="14640" xr2:uid="{E6B1E5AD-2303-4188-98CC-291CCB51BF26}"/>
   </bookViews>
   <sheets>
     <sheet name="Transaction Details" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="83">
-  <si>
-    <t>Transaction Details Generated Monday, May 18, 2026 02:08 AM</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="84">
+  <si>
+    <t>Transaction Details Generated Monday, May 18, 2026 11:01 PM</t>
   </si>
   <si>
     <t>Period</t>
@@ -179,13 +179,16 @@
     <t>0.000</t>
   </si>
   <si>
+    <t xml:space="preserve">07    </t>
+  </si>
+  <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
     <t xml:space="preserve">IDM         </t>
   </si>
   <si>
-    <t xml:space="preserve">612-37713-002            </t>
+    <t xml:space="preserve">612-37713-002                           </t>
   </si>
   <si>
     <t xml:space="preserve">WHS                 </t>
@@ -668,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E29EC4-E911-4B21-AD5C-09B18457F68E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AFA176-E66E-48AA-B344-42C85E410521}">
   <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1149,31 +1152,31 @@
         <v>45</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="X6" s="1">
         <v>-161.6</v>
@@ -1188,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
@@ -1199,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>29</v>
@@ -1271,7 +1274,7 @@
         <v>29</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>29</v>
@@ -1282,7 +1285,7 @@
         <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1368,10 +1371,10 @@
         <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>32</v>
@@ -1389,10 +1392,10 @@
         <v>44</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>34</v>
@@ -1404,13 +1407,13 @@
         <v>35</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>29</v>
@@ -1446,7 +1449,7 @@
         <v>29</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
@@ -1457,7 +1460,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>29</v>
@@ -1529,10 +1532,10 @@
         <v>29</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
@@ -1626,7 +1629,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1798,7 +1801,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1887,7 +1890,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>32</v>
@@ -1905,7 +1908,7 @@
         <v>44</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>33</v>
@@ -1970,10 +1973,10 @@
         <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>32</v>
@@ -1991,7 +1994,7 @@
         <v>44</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>33</v>
@@ -2059,7 +2062,7 @@
         <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>29</v>
@@ -2131,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB17" s="1" t="s">
         <v>37</v>
@@ -2228,7 +2231,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2314,10 +2317,10 @@
         <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>4</v>
@@ -2338,10 +2341,10 @@
         <v>29</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>29</v>
@@ -2403,7 +2406,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>32</v>
@@ -2424,16 +2427,16 @@
         <v>29</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>29</v>
@@ -2572,10 +2575,10 @@
         <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>4</v>
@@ -2596,10 +2599,10 @@
         <v>29</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>29</v>
@@ -2661,7 +2664,7 @@
         <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>32</v>
@@ -2682,7 +2685,7 @@
         <v>29</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>34</v>
